--- a/examples/output/MNL_swissmetro.xlsx
+++ b/examples/output/MNL_swissmetro.xlsx
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="B6">
-        <v>0.7341220378875732</v>
+        <v>0.9549341201782227</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_swissmetro.xlsx
+++ b/examples/output/MNL_swissmetro.xlsx
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="B6">
-        <v>0.9549341201782227</v>
+        <v>0.877830982208252</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_swissmetro.xlsx
+++ b/examples/output/MNL_swissmetro.xlsx
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="B6">
-        <v>0.877830982208252</v>
+        <v>0.8642420768737793</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_swissmetro.xlsx
+++ b/examples/output/MNL_swissmetro.xlsx
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="B6">
-        <v>0.8642420768737793</v>
+        <v>0.8735601902008057</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_swissmetro.xlsx
+++ b/examples/output/MNL_swissmetro.xlsx
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="B6">
-        <v>0.8735601902008057</v>
+        <v>0.8672239780426025</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_swissmetro.xlsx
+++ b/examples/output/MNL_swissmetro.xlsx
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="B6">
-        <v>0.8672239780426025</v>
+        <v>0.965008020401001</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_swissmetro.xlsx
+++ b/examples/output/MNL_swissmetro.xlsx
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="B6">
-        <v>0.965008020401001</v>
+        <v>0.8584508895874023</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_swissmetro.xlsx
+++ b/examples/output/MNL_swissmetro.xlsx
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="B6">
-        <v>0.8584508895874023</v>
+        <v>0.921424150466919</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_swissmetro.xlsx
+++ b/examples/output/MNL_swissmetro.xlsx
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="B6">
-        <v>0.921424150466919</v>
+        <v>0.7995269298553467</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_swissmetro.xlsx
+++ b/examples/output/MNL_swissmetro.xlsx
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="B6">
-        <v>0.7995269298553467</v>
+        <v>0.8161611557006836</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_swissmetro.xlsx
+++ b/examples/output/MNL_swissmetro.xlsx
@@ -486,22 +486,22 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>-0.15463242246824316</v>
+        <v>-0.15463242246824324</v>
       </c>
       <c r="C2">
         <v>0.04323547174247534</v>
       </c>
       <c r="D2">
-        <v>-3.5765175268419553</v>
+        <v>-3.576517526841957</v>
       </c>
       <c r="E2">
         <v>0.0003482019807730108</v>
       </c>
       <c r="F2">
-        <v>0.058163428213987636</v>
+        <v>0.058163428213987615</v>
       </c>
       <c r="G2">
-        <v>-2.6585850802902953</v>
+        <v>-2.658585080290298</v>
       </c>
       <c r="H2">
         <v>0.007846953510272536</v>
@@ -538,22 +538,22 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>-0.7011867124704121</v>
+        <v>-0.7011867124704123</v>
       </c>
       <c r="C4">
-        <v>0.05487393316886619</v>
+        <v>0.054873933168866185</v>
       </c>
       <c r="D4">
-        <v>-12.778138397927783</v>
+        <v>-12.778138397927789</v>
       </c>
       <c r="E4">
         <v>0.0</v>
       </c>
       <c r="F4">
-        <v>0.08256203612404978</v>
+        <v>0.08256203612404973</v>
       </c>
       <c r="G4">
-        <v>-8.492846656747616</v>
+        <v>-8.492846656747624</v>
       </c>
       <c r="H4">
         <v>0.0</v>
@@ -567,19 +567,19 @@
         <v>-1.0837906514857671</v>
       </c>
       <c r="C5">
-        <v>0.05183019168932806</v>
+        <v>0.051830191689328065</v>
       </c>
       <c r="D5">
-        <v>-20.91041179206987</v>
+        <v>-20.910411792069866</v>
       </c>
       <c r="E5">
         <v>0.0</v>
       </c>
       <c r="F5">
-        <v>0.06822505770200239</v>
+        <v>0.0682250577020024</v>
       </c>
       <c r="G5">
-        <v>-15.885521947370345</v>
+        <v>-15.885521947370341</v>
       </c>
       <c r="H5">
         <v>0.0</v>
@@ -590,10 +590,10 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>-1.2778602549029885</v>
+        <v>-1.2778602549029883</v>
       </c>
       <c r="C6">
-        <v>0.056883345268671344</v>
+        <v>0.05688334526867133</v>
       </c>
       <c r="D6">
         <v>-22.46457638641681</v>
@@ -602,10 +602,10 @@
         <v>0.0</v>
       </c>
       <c r="F6">
-        <v>0.10425448374341667</v>
+        <v>0.10425448374341659</v>
       </c>
       <c r="G6">
-        <v>-12.257125152026674</v>
+        <v>-12.257125152026681</v>
       </c>
       <c r="H6">
         <v>0.0</v>
@@ -626,7 +626,7 @@
         <v>13</v>
       </c>
       <c r="B1">
-        <v>-5331.25200691583</v>
+        <v>-5331.252006915831</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="B6">
-        <v>0.8161611557006836</v>
+        <v>0.8101201057434082</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -690,7 +690,7 @@
         <v>22</v>
       </c>
       <c r="B9">
-        <v>10670.50401383166</v>
+        <v>10670.504013831662</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -698,7 +698,7 @@
         <v>23</v>
       </c>
       <c r="B10">
-        <v>10697.783857436803</v>
+        <v>10697.783857436805</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -706,7 +706,7 @@
         <v>24</v>
       </c>
       <c r="B11">
-        <v>0.2345283579630234</v>
+        <v>0.2345283579630233</v>
       </c>
     </row>
   </sheetData>

--- a/examples/output/MNL_swissmetro.xlsx
+++ b/examples/output/MNL_swissmetro.xlsx
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="B6">
-        <v>0.8101201057434082</v>
+        <v>0.8772740364074707</v>
       </c>
     </row>
     <row r="7" spans="1:2">
